--- a/assets/Assets.xlsx
+++ b/assets/Assets.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suren\Documents\UiPath\Forms_uipath\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suren\Documents\UiPath\Forms_uipath\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC48C833-A709-4EB1-8F1B-982EB294035F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39D3055-0DC8-4D42-B6C2-D517C28C596C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3465" yWindow="2535" windowWidth="18000" windowHeight="9270" xr2:uid="{699856C6-E8DA-45ED-8BE8-E3DAC3A09CE5}"/>
   </bookViews>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Value</t>
   </si>
@@ -66,6 +60,24 @@
   </si>
   <si>
     <t>success</t>
+  </si>
+  <si>
+    <t>AssetName</t>
+  </si>
+  <si>
+    <t>AssetType</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>xyx</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>efg</t>
   </si>
 </sst>
 </file>
@@ -437,51 +449,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BBE199-AC3E-4C0D-B064-236745C5158F}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
+      <c r="D4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Assets.xlsx
+++ b/assets/Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suren\Documents\UiPath\Forms_uipath\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39D3055-0DC8-4D42-B6C2-D517C28C596C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21CD5DE-D1E7-41EA-9E24-FF769DED12FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3465" yWindow="2535" windowWidth="18000" windowHeight="9270" xr2:uid="{699856C6-E8DA-45ED-8BE8-E3DAC3A09CE5}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t>Azure_dev</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>uploaded</t>
   </si>
   <si>
@@ -78,6 +75,9 @@
   </si>
   <si>
     <t>efg</t>
+  </si>
+  <si>
+    <t>String</t>
   </si>
 </sst>
 </file>
@@ -454,16 +454,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
         <v>8</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -471,41 +471,41 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
